--- a/templates/BB_ong_thanh_pham.xlsx
+++ b/templates/BB_ong_thanh_pham.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\6. Report NKT XCO-TBDG\NKT Report_2026\NKT-Report\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C6B366B-D993-4B50-AC19-888F12C04879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46E3EFB-2AA3-4239-9D30-B92685A24EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FDF0DB4-5136-426E-A71E-B9C820FDF34D}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="94">
   <si>
     <t>Xưởng Cần ống &amp; Thiết bị đầu giếng - Ban Thiết bị dầu khí - XNCĐ</t>
   </si>
@@ -709,26 +709,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -748,35 +748,35 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1815,26 +1815,26 @@
       <c r="L1" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="81"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -1980,53 +1980,53 @@
       <c r="N9" s="22"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="66" t="s">
+      <c r="E10" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="66" t="s">
+      <c r="F10" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="66" t="s">
+      <c r="G10" s="68" t="s">
         <v>36</v>
       </c>
       <c r="H10" s="59" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="60"/>
-      <c r="J10" s="68" t="s">
+      <c r="J10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="69"/>
-      <c r="L10" s="66" t="s">
+      <c r="K10" s="75"/>
+      <c r="L10" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="M10" s="66" t="s">
+      <c r="M10" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="N10" s="70" t="s">
+      <c r="N10" s="66" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
       <c r="H11" s="24" t="s">
         <v>42</v>
       </c>
@@ -2039,9 +2039,9 @@
       <c r="K11" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="71"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="67"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
@@ -2703,9 +2703,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
-        <v>70</v>
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="26">
+        <v>16</v>
       </c>
       <c r="B28" s="30" t="s">
         <v>70</v>
@@ -2743,9 +2743,9 @@
       </c>
       <c r="N28" s="32"/>
     </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
-        <v>70</v>
+    <row r="29" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="26">
+        <v>17</v>
       </c>
       <c r="B29" s="30" t="s">
         <v>70</v>
@@ -2783,9 +2783,9 @@
       </c>
       <c r="N29" s="32"/>
     </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26" t="s">
-        <v>70</v>
+    <row r="30" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="26">
+        <v>18</v>
       </c>
       <c r="B30" s="30" t="s">
         <v>70</v>
@@ -2823,9 +2823,9 @@
       </c>
       <c r="N30" s="32"/>
     </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
-        <v>70</v>
+    <row r="31" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="26">
+        <v>19</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>70</v>
@@ -2863,9 +2863,9 @@
       </c>
       <c r="N31" s="32"/>
     </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
-        <v>70</v>
+    <row r="32" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="26">
+        <v>20</v>
       </c>
       <c r="B32" s="33" t="s">
         <v>70</v>
@@ -2903,9 +2903,9 @@
       </c>
       <c r="N32" s="32"/>
     </row>
-    <row r="33" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
-        <v>70</v>
+    <row r="33" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="26">
+        <v>21</v>
       </c>
       <c r="B33" s="33" t="s">
         <v>70</v>
@@ -2943,9 +2943,9 @@
       </c>
       <c r="N33" s="32"/>
     </row>
-    <row r="34" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
-        <v>70</v>
+    <row r="34" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="26">
+        <v>22</v>
       </c>
       <c r="B34" s="33" t="s">
         <v>70</v>
@@ -2983,9 +2983,9 @@
       </c>
       <c r="N34" s="32"/>
     </row>
-    <row r="35" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
-        <v>70</v>
+    <row r="35" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="26">
+        <v>23</v>
       </c>
       <c r="B35" s="33" t="s">
         <v>70</v>
@@ -3023,9 +3023,9 @@
       </c>
       <c r="N35" s="32"/>
     </row>
-    <row r="36" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="26" t="s">
-        <v>70</v>
+    <row r="36" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="26">
+        <v>24</v>
       </c>
       <c r="B36" s="33" t="s">
         <v>70</v>
@@ -3063,9 +3063,9 @@
       </c>
       <c r="N36" s="32"/>
     </row>
-    <row r="37" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
-        <v>70</v>
+    <row r="37" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="26">
+        <v>25</v>
       </c>
       <c r="B37" s="33" t="s">
         <v>70</v>
@@ -3103,9 +3103,9 @@
       </c>
       <c r="N37" s="32"/>
     </row>
-    <row r="38" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26" t="s">
-        <v>70</v>
+    <row r="38" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="26">
+        <v>26</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>70</v>
@@ -3143,9 +3143,9 @@
       </c>
       <c r="N38" s="32"/>
     </row>
-    <row r="39" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
-        <v>70</v>
+    <row r="39" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="26">
+        <v>27</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>70</v>
@@ -3183,9 +3183,9 @@
       </c>
       <c r="N39" s="32"/>
     </row>
-    <row r="40" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
-        <v>70</v>
+    <row r="40" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="26">
+        <v>28</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>70</v>
@@ -3223,9 +3223,9 @@
       </c>
       <c r="N40" s="32"/>
     </row>
-    <row r="41" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
-        <v>70</v>
+    <row r="41" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="26">
+        <v>29</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>70</v>
@@ -3263,9 +3263,9 @@
       </c>
       <c r="N41" s="32"/>
     </row>
-    <row r="42" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
-        <v>70</v>
+    <row r="42" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="26">
+        <v>30</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>70</v>
@@ -3303,9 +3303,9 @@
       </c>
       <c r="N42" s="32"/>
     </row>
-    <row r="43" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="26" t="s">
-        <v>70</v>
+    <row r="43" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="26">
+        <v>31</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>70</v>
@@ -3343,9 +3343,9 @@
       </c>
       <c r="N43" s="32"/>
     </row>
-    <row r="44" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
-        <v>70</v>
+    <row r="44" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="26">
+        <v>32</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>70</v>
@@ -3383,9 +3383,9 @@
       </c>
       <c r="N44" s="32"/>
     </row>
-    <row r="45" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
-        <v>70</v>
+    <row r="45" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="26">
+        <v>33</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>70</v>
@@ -3423,9 +3423,9 @@
       </c>
       <c r="N45" s="32"/>
     </row>
-    <row r="46" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="26" t="s">
-        <v>70</v>
+    <row r="46" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="26">
+        <v>34</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>70</v>
@@ -3463,9 +3463,9 @@
       </c>
       <c r="N46" s="32"/>
     </row>
-    <row r="47" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="26" t="s">
-        <v>70</v>
+    <row r="47" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="26">
+        <v>35</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>70</v>
@@ -3503,9 +3503,9 @@
       </c>
       <c r="N47" s="32"/>
     </row>
-    <row r="48" spans="1:14" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="26" t="s">
-        <v>70</v>
+    <row r="48" spans="1:14" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="26">
+        <v>36</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>70</v>
@@ -3543,9 +3543,9 @@
       </c>
       <c r="N48" s="32"/>
     </row>
-    <row r="49" spans="1:28" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="26" t="s">
-        <v>70</v>
+    <row r="49" spans="1:28" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="26">
+        <v>37</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>70</v>
@@ -3583,9 +3583,9 @@
       </c>
       <c r="N49" s="32"/>
     </row>
-    <row r="50" spans="1:28" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="26" t="s">
-        <v>70</v>
+    <row r="50" spans="1:28" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="26">
+        <v>38</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>70</v>
@@ -3623,9 +3623,9 @@
       </c>
       <c r="N50" s="32"/>
     </row>
-    <row r="51" spans="1:28" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="26" t="s">
-        <v>70</v>
+    <row r="51" spans="1:28" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="26">
+        <v>39</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>70</v>
@@ -3663,9 +3663,9 @@
       </c>
       <c r="N51" s="32"/>
     </row>
-    <row r="52" spans="1:28" s="2" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="26" t="s">
-        <v>70</v>
+    <row r="52" spans="1:28" s="2" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="26">
+        <v>40</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>70</v>
@@ -3779,19 +3779,19 @@
       <c r="N55" s="14"/>
     </row>
     <row r="56" spans="1:28" s="2" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
-      <c r="F56" s="58"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="58"/>
-      <c r="J56" s="58"/>
-      <c r="K56" s="58"/>
-      <c r="L56" s="58"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
     </row>
@@ -3890,34 +3890,34 @@
       <c r="N61" s="10"/>
     </row>
     <row r="62" spans="1:28" s="42" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="50" t="s">
+      <c r="A62" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="B62" s="50"/>
-      <c r="C62" s="50"/>
-      <c r="D62" s="50"/>
-      <c r="E62" s="50"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="50"/>
-      <c r="H62" s="50"/>
-      <c r="I62" s="50"/>
-      <c r="J62" s="50"/>
-      <c r="K62" s="50"/>
-      <c r="L62" s="50"/>
-      <c r="M62" s="50"/>
-      <c r="N62" s="50"/>
-      <c r="Q62" s="51"/>
-      <c r="R62" s="52"/>
-      <c r="S62" s="53"/>
-      <c r="T62" s="54"/>
-      <c r="U62" s="53"/>
-      <c r="V62" s="53"/>
-      <c r="W62" s="55"/>
-      <c r="X62" s="53"/>
-      <c r="Y62" s="53"/>
-      <c r="Z62" s="55"/>
-      <c r="AA62" s="53"/>
-      <c r="AB62" s="53"/>
+      <c r="B62" s="55"/>
+      <c r="C62" s="55"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="55"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="55"/>
+      <c r="I62" s="55"/>
+      <c r="J62" s="55"/>
+      <c r="K62" s="55"/>
+      <c r="L62" s="55"/>
+      <c r="M62" s="55"/>
+      <c r="N62" s="55"/>
+      <c r="Q62" s="56"/>
+      <c r="R62" s="57"/>
+      <c r="S62" s="51"/>
+      <c r="T62" s="58"/>
+      <c r="U62" s="51"/>
+      <c r="V62" s="51"/>
+      <c r="W62" s="50"/>
+      <c r="X62" s="51"/>
+      <c r="Y62" s="51"/>
+      <c r="Z62" s="50"/>
+      <c r="AA62" s="51"/>
+      <c r="AB62" s="51"/>
     </row>
     <row r="63" spans="1:28" s="42" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="45"/>
@@ -3968,43 +3968,43 @@
       <c r="N65" s="47"/>
     </row>
     <row r="66" spans="1:28" s="42" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="50"/>
-      <c r="C66" s="50"/>
-      <c r="D66" s="50"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="50"/>
-      <c r="H66" s="50"/>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="50"/>
-      <c r="M66" s="50"/>
-      <c r="N66" s="50"/>
-      <c r="Q66" s="51"/>
-      <c r="R66" s="52"/>
-      <c r="S66" s="53"/>
-      <c r="T66" s="54"/>
-      <c r="U66" s="53"/>
-      <c r="V66" s="53"/>
-      <c r="W66" s="55"/>
-      <c r="X66" s="53"/>
-      <c r="Y66" s="53"/>
-      <c r="Z66" s="55"/>
-      <c r="AA66" s="53"/>
-      <c r="AB66" s="53"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="55"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="G66" s="55"/>
+      <c r="H66" s="55"/>
+      <c r="I66" s="55"/>
+      <c r="J66" s="55"/>
+      <c r="K66" s="55"/>
+      <c r="L66" s="55"/>
+      <c r="M66" s="55"/>
+      <c r="N66" s="55"/>
+      <c r="Q66" s="56"/>
+      <c r="R66" s="57"/>
+      <c r="S66" s="51"/>
+      <c r="T66" s="58"/>
+      <c r="U66" s="51"/>
+      <c r="V66" s="51"/>
+      <c r="W66" s="50"/>
+      <c r="X66" s="51"/>
+      <c r="Y66" s="51"/>
+      <c r="Z66" s="50"/>
+      <c r="AA66" s="51"/>
+      <c r="AB66" s="51"/>
     </row>
     <row r="67" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="N67" s="48"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="M68" s="56">
+      <c r="M68" s="52">
         <v>26122016</v>
       </c>
-      <c r="N68" s="56"/>
+      <c r="N68" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -4014,6 +4014,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:M9"/>
+    <mergeCell ref="B55:L55"/>
     <mergeCell ref="N10:N11"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
@@ -4026,14 +4027,13 @@
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="L10:L11"/>
     <mergeCell ref="M10:M11"/>
-    <mergeCell ref="W62:Y62"/>
-    <mergeCell ref="Z62:AB62"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="D13:D52"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="W66:Y66"/>
+    <mergeCell ref="Z66:AB66"/>
     <mergeCell ref="M68:N68"/>
     <mergeCell ref="B56:L56"/>
     <mergeCell ref="A62:N62"/>
@@ -4042,8 +4042,8 @@
     <mergeCell ref="A66:N66"/>
     <mergeCell ref="Q66:S66"/>
     <mergeCell ref="T66:V66"/>
-    <mergeCell ref="W66:Y66"/>
-    <mergeCell ref="Z66:AB66"/>
+    <mergeCell ref="W62:Y62"/>
+    <mergeCell ref="Z62:AB62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.3" header="0.3" footer="0.05"/>
